--- a/entrepreneuriat/kpi-suivi.xlsx
+++ b/entrepreneuriat/kpi-suivi.xlsx
@@ -1400,7 +1400,9 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="23">
         <f>IF(AND(ISNUMBER(F2),F2&gt;0,ISNUMBER(I2)),I2/F2,"")</f>
@@ -1410,7 +1412,7 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Baseline relevée le 15/10/2026 (à relever)</t>
+          <t>15/10/2026 : aucune page LinkedIn Syntheza n’existe, à créer avant le 22/10</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
@@ -1530,7 +1532,9 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
+      <c r="H4" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="23">
         <f>IF(AND(ISNUMBER(F4),F4&gt;0,ISNUMBER(I4)),I4/F4,"")</f>
@@ -1540,7 +1544,7 @@
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Baseline relevée le 15/10/2026 (à relever)</t>
+          <t>@syntheza.eip relevé le 15/10/2026 sur le profil public : 5 abonnés, 6 publications au total, 0 abonnement. Impressions, reach et engagements à relever dans les statistiques du compte</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
@@ -5787,10 +5791,8 @@
           <t>Gain net vs baseline</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>à relever</t>
-        </is>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>25</v>
@@ -5875,10 +5877,8 @@
           <t>Gain net vs baseline</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>à relever</t>
-        </is>
+      <c r="D15" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>15</v>
